--- a/docs/downloads/经营分_鲁西省区__泰安片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_鲁西省区__泰安片区_2026-10-18.xlsx
@@ -863,33 +863,33 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>7298602763288578087</t>
+          <t>6601144159053023235</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店（泰安高铁站店）</t>
+          <t>麗枫酒店(泰安东平体育会展中心白佛山店)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>白玉兰酒店(泰安高铁站店)</t>
+          <t>麗枫酒店(泰安东平体育会展中心白佛山店)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I4" t="n">
-        <v>-5</v>
+        <v>-13</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -899,19 +899,19 @@
         <v>10</v>
       </c>
       <c r="M4" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="N4" t="n">
         <v>30</v>
       </c>
       <c r="O4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P4" t="n">
         <v>30</v>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R4" t="n">
         <v>30</v>
@@ -951,17 +951,17 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>6897707448426039296</t>
+          <t>7236623109233575951</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>喆啡酒店（泰安万达广场汽车站店）</t>
+          <t>7天酒店（泰安市政广场店）</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>喆啡酒店(泰安万达广场汽车站店)</t>
+          <t>7天酒店(泰安市政广场店)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -973,11 +973,11 @@
         <v>90</v>
       </c>
       <c r="I5" t="n">
-        <v>-15</v>
+        <v>5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -987,19 +987,19 @@
         <v>10</v>
       </c>
       <c r="M5" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N5" t="n">
         <v>30</v>
       </c>
       <c r="O5" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P5" t="n">
         <v>30</v>
       </c>
       <c r="Q5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R5" t="n">
         <v>30</v>
@@ -1039,29 +1039,29 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>6601144159053023235</t>
+          <t>6897707448426039296</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>麗枫酒店(泰安东平体育会展中心白佛山店)</t>
+          <t>喆啡酒店（泰安万达广场汽车站店）</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>麗枫酒店(泰安东平体育会展中心白佛山店)</t>
+          <t>喆啡酒店(泰安万达广场汽车站店)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I6" t="n">
-        <v>-8</v>
+        <v>-15</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>10</v>
       </c>
       <c r="M6" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="N6" t="n">
         <v>30</v>
@@ -1087,7 +1087,7 @@
         <v>30</v>
       </c>
       <c r="Q6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="R6" t="n">
         <v>30</v>
@@ -1127,17 +1127,17 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>7236623109233575951</t>
+          <t>7298602763288578087</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7天酒店（泰安市政广场店）</t>
+          <t>白玉兰商务酒店（泰安高铁站店）</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>7天酒店(泰安市政广场店)</t>
+          <t>白玉兰酒店(泰安高铁站店)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1146,14 +1146,14 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -1163,13 +1163,13 @@
         <v>10</v>
       </c>
       <c r="M7" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="N7" t="n">
         <v>30</v>
       </c>
       <c r="O7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P7" t="n">
         <v>30</v>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>7431066212282402855</t>
+          <t>7482309706292135947</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>希岸酒店（泰安泰山风景区岱庙店）</t>
+          <t>喆啡酒店（泰安泰山景区天外村店）</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>希岸酒店(泰安泰山风景区岱庙店)</t>
+          <t>喆啡酒店(泰安泰山景区天外村店)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>7372376284489320489</t>
+          <t>7431066212282402855</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>泰安泰山天平湖非繁云居酒店</t>
+          <t>希岸酒店（泰安泰山风景区岱庙店）</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>泰山天平湖云居酒店</t>
+          <t>希岸酒店(泰安泰山风景区岱庙店)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1339,19 +1339,19 @@
         <v>10</v>
       </c>
       <c r="M9" t="n">
+        <v>25</v>
+      </c>
+      <c r="N9" t="n">
+        <v>30</v>
+      </c>
+      <c r="O9" t="n">
+        <v>25</v>
+      </c>
+      <c r="P9" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q9" t="n">
         <v>15</v>
-      </c>
-      <c r="N9" t="n">
-        <v>30</v>
-      </c>
-      <c r="O9" t="n">
-        <v>30</v>
-      </c>
-      <c r="P9" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>20</v>
       </c>
       <c r="R9" t="n">
         <v>30</v>
@@ -1391,17 +1391,17 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>6601141127011633166</t>
+          <t>7372376284489320489</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>潮漫酒店（泰安东岳大街岱庙店）</t>
+          <t>泰安泰山天平湖非繁云居酒店</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>潮漫酒店(泰安东岳大街岱庙店)</t>
+          <t>泰山天平湖云居酒店</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1413,11 +1413,11 @@
         <v>95</v>
       </c>
       <c r="I10" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1427,19 +1427,19 @@
         <v>10</v>
       </c>
       <c r="M10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="N10" t="n">
         <v>30</v>
       </c>
       <c r="O10" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P10" t="n">
         <v>30</v>
       </c>
       <c r="Q10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R10" t="n">
         <v>30</v>
@@ -1479,17 +1479,17 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>7301176941552338970</t>
+          <t>6601141127011633166</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店(泰安泰山站店)</t>
+          <t>潮漫酒店（泰安东岳大街岱庙店）</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店(泰安泰山站店)</t>
+          <t>潮漫酒店(泰安东岳大街岱庙店)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1501,11 +1501,11 @@
         <v>95</v>
       </c>
       <c r="I11" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1515,19 +1515,19 @@
         <v>10</v>
       </c>
       <c r="M11" t="n">
+        <v>25</v>
+      </c>
+      <c r="N11" t="n">
+        <v>30</v>
+      </c>
+      <c r="O11" t="n">
+        <v>25</v>
+      </c>
+      <c r="P11" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q11" t="n">
         <v>15</v>
-      </c>
-      <c r="N11" t="n">
-        <v>30</v>
-      </c>
-      <c r="O11" t="n">
-        <v>30</v>
-      </c>
-      <c r="P11" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>20</v>
       </c>
       <c r="R11" t="n">
         <v>30</v>
@@ -1567,17 +1567,17 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>7234796907959158843</t>
+          <t>7301176941552338970</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>麗枫酒店(泰安肥城泰西大街店)</t>
+          <t>白玉兰商务酒店(泰安泰山站店)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>麗枫酒店(泰安肥城泰西大街店)</t>
+          <t>白玉兰商务酒店(泰安泰山站店)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1589,11 +1589,11 @@
         <v>95</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1603,13 +1603,13 @@
         <v>10</v>
       </c>
       <c r="M12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="N12" t="n">
         <v>30</v>
       </c>
       <c r="O12" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P12" t="n">
         <v>30</v>
@@ -1655,17 +1655,17 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>7107794618372884487</t>
+          <t>7234796907959158843</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>麗枫酒店（泰安岱阳大街店）</t>
+          <t>麗枫酒店(泰安肥城泰西大街店)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>麗枫酒店(泰安岱阳大街店)</t>
+          <t>麗枫酒店(泰安肥城泰西大街店)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1674,7 +1674,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1691,13 +1691,13 @@
         <v>10</v>
       </c>
       <c r="M13" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N13" t="n">
         <v>30</v>
       </c>
       <c r="O13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P13" t="n">
         <v>30</v>
@@ -1743,17 +1743,17 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>7482309706292135947</t>
+          <t>7107794618372884487</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>喆啡酒店（泰安泰山景区天外村店）</t>
+          <t>麗枫酒店（泰安岱阳大街店）</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>喆啡酒店(泰安泰山景区天外村店)</t>
+          <t>麗枫酒店(泰安岱阳大街店)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1762,14 +1762,14 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1779,19 +1779,19 @@
         <v>10</v>
       </c>
       <c r="M14" t="n">
+        <v>22</v>
+      </c>
+      <c r="N14" t="n">
+        <v>30</v>
+      </c>
+      <c r="O14" t="n">
         <v>25</v>
       </c>
-      <c r="N14" t="n">
-        <v>30</v>
-      </c>
-      <c r="O14" t="n">
-        <v>30</v>
-      </c>
       <c r="P14" t="n">
         <v>30</v>
       </c>
       <c r="Q14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R14" t="n">
         <v>30</v>
@@ -1941,7 +1941,7 @@
         <v>100</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -2095,17 +2095,17 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>6884924369257236487</t>
+          <t>7233388515944302631</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>7天优品（泰安宁阳县政府广场店）</t>
+          <t>维也纳智好酒店(泰安泰山景区天外村店)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>7天优品(泰安宁阳县政府广场店)</t>
+          <t>维也纳智好酒店(泰山景区天外村店)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2114,14 +2114,14 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -2131,7 +2131,7 @@
         <v>10</v>
       </c>
       <c r="M18" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N18" t="n">
         <v>30</v>
@@ -2143,7 +2143,7 @@
         <v>30</v>
       </c>
       <c r="Q18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="R18" t="n">
         <v>30</v>
@@ -2183,17 +2183,17 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>7477820810032318504</t>
+          <t>6884924369257236487</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店（泰安新泰青云购物中心金斗路店）</t>
+          <t>7天优品（泰安宁阳县政府广场店）</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店(泰安新泰青云购物中心金斗路店)</t>
+          <t>7天优品(泰安宁阳县政府广场店)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -2219,19 +2219,19 @@
         <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N19" t="n">
         <v>30</v>
       </c>
       <c r="O19" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P19" t="n">
         <v>30</v>
       </c>
       <c r="Q19" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="R19" t="n">
         <v>30</v>
@@ -2271,17 +2271,17 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>6886775023332362240</t>
+          <t>7477820810032318504</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店（肥城新华大厦店）</t>
+          <t>白玉兰商务酒店（泰安新泰青云购物中心金斗路店）</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>白玉兰(商务)酒店(肥城新华大厦店)</t>
+          <t>白玉兰商务酒店(泰安新泰青云购物中心金斗路店)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2447,22 +2447,22 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>6948542184782039081</t>
+          <t>7512768267102980115</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（山东泰安万达广场店）</t>
+          <t>维也纳酒店(5.0宁阳政府广场宁阳大道店)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(山东泰安万达广场店)</t>
+          <t>维也纳酒店(宁阳政府宁阳大道人民广场店)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -2483,13 +2483,13 @@
         <v>10</v>
       </c>
       <c r="M22" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N22" t="n">
         <v>30</v>
       </c>
       <c r="O22" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P22" t="n">
         <v>30</v>
@@ -2535,17 +2535,17 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>7233388515944302631</t>
+          <t>6601171431122274318</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>维也纳智好酒店(泰安泰山景区天外村店)</t>
+          <t>锦江之星酒店（泰安泰山火车站店）</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>维也纳智好酒店(泰山景区天外村店)</t>
+          <t>锦江之星(泰安泰山火车站店)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -2571,7 +2571,7 @@
         <v>10</v>
       </c>
       <c r="M23" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N23" t="n">
         <v>30</v>
@@ -2583,7 +2583,7 @@
         <v>30</v>
       </c>
       <c r="Q23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R23" t="n">
         <v>30</v>
@@ -2623,33 +2623,33 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>7512768267102980115</t>
+          <t>7447076702268459045</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>维也纳酒店(5.0宁阳政府广场宁阳大道店)</t>
+          <t>麗枫酒店（泰安万达广场店）</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>维也纳酒店(宁阳政府宁阳大道人民广场店)</t>
+          <t>麗枫酒店(泰安万达广场店)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H24" t="n">
         <v>105</v>
       </c>
       <c r="I24" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -2665,13 +2665,13 @@
         <v>30</v>
       </c>
       <c r="O24" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P24" t="n">
         <v>30</v>
       </c>
       <c r="Q24" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R24" t="n">
         <v>30</v>
@@ -2711,17 +2711,17 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>6601171431122274318</t>
+          <t>7012814693009983495</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>锦江之星酒店（泰安泰山火车站店）</t>
+          <t>7天优品Premium（泰安肥城石横镇政府店）</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>锦江之星(泰安泰山火车站店)</t>
+          <t>7天优品Premium(泰安肥城石横镇政府店)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2730,14 +2730,14 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -2747,7 +2747,7 @@
         <v>10</v>
       </c>
       <c r="M25" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N25" t="n">
         <v>30</v>
@@ -2799,17 +2799,17 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>7447076702268459045</t>
+          <t>6601145782395471885</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>麗枫酒店（泰安万达广场店）</t>
+          <t>7天酒店（泰安东平西华联店）</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>麗枫酒店(泰安万达广场店)</t>
+          <t>7天连锁酒店(泰安东平西华联店)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2818,14 +2818,14 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -2835,7 +2835,7 @@
         <v>10</v>
       </c>
       <c r="M26" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N26" t="n">
         <v>30</v>
@@ -2887,17 +2887,17 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>7012814693009983495</t>
+          <t>7616275361281607695</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>7天优品Premium（泰安肥城石横镇政府店）</t>
+          <t>白玉兰商务酒店（泰安高铁财金时代广场店）</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>7天优品Premium(泰安肥城石横镇政府店)</t>
+          <t>白玉兰酒店(泰安高铁财金时代广场店)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2923,13 +2923,13 @@
         <v>10</v>
       </c>
       <c r="M27" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N27" t="n">
         <v>30</v>
       </c>
       <c r="O27" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P27" t="n">
         <v>30</v>
@@ -2975,17 +2975,17 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>6601145782395471885</t>
+          <t>6886775023332362240</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>7天酒店（泰安东平西华联店）</t>
+          <t>白玉兰商务酒店（肥城新华大厦店）</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>7天连锁酒店(泰安东平西华联店)</t>
+          <t>白玉兰(商务)酒店(肥城新华大厦店)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2997,11 +2997,11 @@
         <v>110</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -3017,13 +3017,13 @@
         <v>30</v>
       </c>
       <c r="O28" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P28" t="n">
         <v>30</v>
       </c>
       <c r="Q28" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R28" t="n">
         <v>30</v>
@@ -3063,33 +3063,33 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>7616275361281607695</t>
+          <t>6948542184782039081</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店（泰安高铁财金时代广场店）</t>
+          <t>维也纳国际酒店（山东泰安万达广场店）</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>白玉兰酒店(泰安高铁财金时代广场店)</t>
+          <t>维也纳国际酒店(山东泰安万达广场店)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H29" t="n">
         <v>110</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -3099,13 +3099,13 @@
         <v>10</v>
       </c>
       <c r="M29" t="n">
+        <v>30</v>
+      </c>
+      <c r="N29" t="n">
+        <v>30</v>
+      </c>
+      <c r="O29" t="n">
         <v>25</v>
-      </c>
-      <c r="N29" t="n">
-        <v>30</v>
-      </c>
-      <c r="O29" t="n">
-        <v>30</v>
       </c>
       <c r="P29" t="n">
         <v>30</v>
@@ -3789,7 +3789,7 @@
         <v>115</v>
       </c>
       <c r="I37" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
